--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/post FET_HRM-2031-0392/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/post FET_HRM-2031-0392/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
@@ -413,28 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="C1" t="inlineStr">
         <is>
-          <t>Distance 1</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Distance 2</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Angle</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -446,20 +456,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fiducial 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>123.45854</v>
+        <v>17.15615</v>
       </c>
       <c r="D2" t="n">
-        <v>87.36148</v>
+        <v>16.57376</v>
       </c>
       <c r="E2" t="n">
-        <v>92.66783</v>
-      </c>
-      <c r="F2" t="n">
-        <v>523.22145</v>
+        <v>16.84248</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05062</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.84428</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +482,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>119.73956</v>
+        <v>17.13212</v>
       </c>
       <c r="D3" t="n">
-        <v>85.78937999999999</v>
+        <v>16.76832</v>
       </c>
       <c r="E3" t="n">
-        <v>90.64868</v>
+        <v>16.82724</v>
       </c>
       <c r="F3" t="n">
-        <v>515.12504</v>
+        <v>42.9264</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.82519</v>
       </c>
     </row>
     <row r="4">
@@ -487,17 +506,25 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>122.16684</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>85.11887</v>
+        <v>16.74855</v>
       </c>
       <c r="E4" t="n">
-        <v>92.10509</v>
+        <v>16.86183</v>
       </c>
       <c r="F4" t="n">
-        <v>509.86064</v>
+        <v>42.56838</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.05166</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.84593</v>
       </c>
     </row>
     <row r="5">
@@ -506,17 +533,25 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>122.08792</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12,5</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>88.30924</v>
+        <v>16.49643</v>
       </c>
       <c r="E5" t="n">
-        <v>92.91659</v>
+        <v>16.72564</v>
       </c>
       <c r="F5" t="n">
-        <v>521.08833</v>
+        <v>42.32915</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05133</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.85696</v>
       </c>
     </row>
     <row r="6">
@@ -526,16 +561,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>120.24886</v>
+        <v>17.07169</v>
       </c>
       <c r="D6" t="n">
-        <v>85.14039</v>
+        <v>16.7468</v>
       </c>
       <c r="E6" t="n">
-        <v>90.58718</v>
+        <v>16.80215</v>
       </c>
       <c r="F6" t="n">
-        <v>519.45416</v>
+        <v>43.58495</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.05057</v>
+      </c>
+      <c r="H6" t="e">
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +586,24 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>123.08416</v>
+        <v>16.80573</v>
       </c>
       <c r="D7" t="n">
-        <v>84.83506</v>
-      </c>
-      <c r="E7" t="n">
-        <v>90.63181</v>
+        <v>16.61515</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 16.48 </t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>513.33978</v>
+        <v>42.26171</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05122</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.86547</v>
       </c>
     </row>
     <row r="8">
@@ -564,16 +613,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>118.93879</v>
+        <v>16.76454</v>
       </c>
       <c r="D8" t="n">
-        <v>85.29707000000001</v>
+        <v>16.42205</v>
       </c>
       <c r="E8" t="n">
-        <v>91.01562</v>
+        <v>16.60929</v>
       </c>
       <c r="F8" t="n">
-        <v>526.04072</v>
+        <v>42.27759</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.05067</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.85687</v>
       </c>
     </row>
     <row r="9">
@@ -583,16 +638,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>122.81859</v>
+        <v>17.0223</v>
       </c>
       <c r="D9" t="n">
-        <v>84.76316</v>
+        <v>16.61211</v>
       </c>
       <c r="E9" t="n">
-        <v>92.48547000000001</v>
+        <v>17.01935</v>
       </c>
       <c r="F9" t="n">
-        <v>527.47782</v>
+        <v>42.97039</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.85374</v>
       </c>
     </row>
     <row r="10">
@@ -602,27 +663,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>120.72957</v>
+        <v>17.16318</v>
       </c>
       <c r="D10" t="n">
-        <v>88.04244</v>
+        <v>16.4237</v>
       </c>
       <c r="E10" t="n">
-        <v>91.95734</v>
+        <v>16.66152</v>
       </c>
       <c r="F10" t="n">
-        <v>529.71342</v>
+        <v>42.45924</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05049</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.80314</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Height</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Diameter</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -634,14 +701,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Micro Bump 3</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.94605</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>24.44697</v>
+        <v>1.13944</v>
       </c>
     </row>
     <row r="13">
@@ -651,10 +718,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.381449999999999</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>24.35194</v>
+        <v>1.10316</v>
       </c>
     </row>
     <row r="14">
@@ -664,10 +731,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.70472</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>25.15897</v>
+        <v>1.09549</v>
       </c>
     </row>
     <row r="15">
@@ -677,10 +744,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.7171</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>25.25032</v>
+        <v>1.11092</v>
       </c>
     </row>
     <row r="16">
@@ -690,10 +757,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.68008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>24.21619</v>
+        <v>1.10603</v>
       </c>
     </row>
     <row r="17">
@@ -703,10 +770,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.6693</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>24.28951</v>
+        <v>1.14664</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +783,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.60549</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>24.05234</v>
+        <v>1.11768</v>
       </c>
     </row>
     <row r="19">
@@ -729,10 +796,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.85383</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>24.45358</v>
+        <v>1.10016</v>
       </c>
     </row>
     <row r="20">
@@ -742,272 +809,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.61477</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>24.40458</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>16.79342</v>
-      </c>
-      <c r="D22" t="n">
-        <v>17.00512</v>
-      </c>
-      <c r="E22" t="n">
-        <v>16.98242</v>
-      </c>
-      <c r="F22" t="n">
-        <v>41.62726</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.05137</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.82165</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>17.17426</v>
-      </c>
-      <c r="D23" t="n">
-        <v>16.93589</v>
-      </c>
-      <c r="E23" t="n">
-        <v>17.07803</v>
-      </c>
-      <c r="F23" t="n">
-        <v>41.8881</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.0512</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.78785</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>17.02373</v>
-      </c>
-      <c r="D24" t="n">
-        <v>17.0593</v>
-      </c>
-      <c r="E24" t="n">
-        <v>16.82889</v>
-      </c>
-      <c r="F24" t="n">
-        <v>41.85114</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.05061</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.81863</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>17.28158</v>
-      </c>
-      <c r="D25" t="n">
-        <v>17.14506</v>
-      </c>
-      <c r="E25" t="n">
-        <v>16.56929</v>
-      </c>
-      <c r="F25" t="n">
-        <v>42.86517</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.0509</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.78963</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>16.72691</v>
-      </c>
-      <c r="D26" t="n">
-        <v>16.47313</v>
-      </c>
-      <c r="E26" t="n">
-        <v>17.04317</v>
-      </c>
-      <c r="F26" t="n">
-        <v>42.6205</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.0505</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.8143</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>16.67459</v>
-      </c>
-      <c r="D27" t="n">
-        <v>16.87942</v>
-      </c>
-      <c r="E27" t="n">
-        <v>16.78258</v>
-      </c>
-      <c r="F27" t="n">
-        <v>42.73218</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.0511</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.82165</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>16.98224</v>
-      </c>
-      <c r="D28" t="n">
-        <v>16.55012</v>
-      </c>
-      <c r="E28" t="n">
-        <v>16.64293</v>
-      </c>
-      <c r="F28" t="n">
-        <v>42.69944</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.05187</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.84663</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>16.61906</v>
-      </c>
-      <c r="D29" t="n">
-        <v>16.59505</v>
-      </c>
-      <c r="E29" t="n">
-        <v>16.91103</v>
-      </c>
-      <c r="F29" t="n">
-        <v>43.4395</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.05092</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.82547</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>16.67925</v>
-      </c>
-      <c r="D30" t="n">
-        <v>16.50899</v>
-      </c>
-      <c r="E30" t="n">
-        <v>16.66093</v>
-      </c>
-      <c r="F30" t="n">
-        <v>42.94026</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.05076</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.88397</v>
+        <v>1.12053</v>
       </c>
     </row>
   </sheetData>
